--- a/Analysis_and_Visualization/data/data.xlsx
+++ b/Analysis_and_Visualization/data/data.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\research\2026-SLR-regression-testing-optimization\Analysis_and_Visualization\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED3C1B6-BEB9-4651-AB7D-64CFD72E2A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29FCEC5-B88B-4D44-849C-ABACC48290A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1344" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="6" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="3" activeTab="3" xr2:uid="{FF880EED-EA60-9E49-B15D-179496B980D1}"/>
   </bookViews>
   <sheets>
     <sheet name="data_extraction" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId2"/>
     <sheet name="RQ1_trends_by_category_per_year" sheetId="3" r:id="rId3"/>
-    <sheet name="RQ1_replicability_per_year" sheetId="5" r:id="rId4"/>
-    <sheet name="RQ2_p_taxonomy_vs_algorithm" sheetId="4" r:id="rId5"/>
-    <sheet name="RQ2_s_taxonomy_vs_algorithm" sheetId="6" r:id="rId6"/>
-    <sheet name="RQ3_datasets" sheetId="8" r:id="rId7"/>
-    <sheet name="raw_data" sheetId="1" r:id="rId8"/>
+    <sheet name="classification_by_venue_q" sheetId="9" r:id="rId4"/>
+    <sheet name="RQ1_replicability_per_year" sheetId="5" r:id="rId5"/>
+    <sheet name="RQ2_p_taxonomy_vs_algorithm" sheetId="4" r:id="rId6"/>
+    <sheet name="RQ2_s_taxonomy_vs_algorithm" sheetId="6" r:id="rId7"/>
+    <sheet name="RQ3_datasets" sheetId="8" r:id="rId8"/>
+    <sheet name="raw_data" sheetId="1" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4036" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4049" uniqueCount="1421">
   <si>
     <t>ID</t>
   </si>
@@ -4533,6 +4534,12 @@
   </si>
   <si>
     <t>Apache Projects</t>
+  </si>
+  <si>
+    <t>pubtype</t>
+  </si>
+  <si>
+    <t>IDQ</t>
   </si>
 </sst>
 </file>
@@ -19571,6 +19578,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DB092F88-9A5B-4AC3-90D9-2AD8211489DF}" name="Table7" displayName="Table7" ref="A7:C17" totalsRowShown="0">
+  <autoFilter ref="A7:C17" xr:uid="{DB092F88-9A5B-4AC3-90D9-2AD8211489DF}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00158DF4-E73B-4085-8AAC-4740524C9315}" name="pubtype"/>
+    <tableColumn id="2" xr3:uid="{8509A622-C333-47D9-88E3-9AD94BC03BBC}" name="IDQ"/>
+    <tableColumn id="3" xr3:uid="{9594B068-D73C-4369-A503-D8445C863056}" name="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2041F714-787B-4DF5-952C-18709ACBB07F}" name="Table4" displayName="Table4" ref="A1:D14" totalsRowShown="0">
   <autoFilter ref="A1:D14" xr:uid="{2041F714-787B-4DF5-952C-18709ACBB07F}"/>
   <tableColumns count="4">
@@ -19583,7 +19602,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A9482A75-67B8-4348-A128-516A03A72ACC}" name="Table3" displayName="Table3" ref="A1:G11" totalsRowShown="0">
   <autoFilter ref="A1:G11" xr:uid="{A9482A75-67B8-4348-A128-516A03A72ACC}"/>
   <tableColumns count="7">
@@ -19599,7 +19618,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7C9868C9-B826-4E6A-928E-C718CF0D61DD}" name="Table5" displayName="Table5" ref="A1:G5" totalsRowShown="0">
   <autoFilter ref="A1:G5" xr:uid="{7C9868C9-B826-4E6A-928E-C718CF0D61DD}"/>
   <tableColumns count="7">
@@ -19615,7 +19634,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{60427D65-C1BB-4033-B0DD-E94497FE33A0}" name="Table6" displayName="Table6" ref="A1:C11" totalsRowShown="0">
   <autoFilter ref="A1:C11" xr:uid="{60427D65-C1BB-4033-B0DD-E94497FE33A0}"/>
   <tableColumns count="3">
@@ -27590,204 +27609,132 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A6ACA0-5BAF-4CF3-A9BA-46A30A6E0A57}">
-  <dimension ref="A1:D14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F84B76-726E-4128-BAFC-133CC56F4C2B}">
+  <dimension ref="A7:C17"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="9.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1413</v>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1403</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>2013</v>
-      </c>
-      <c r="B2">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9">
+        <v>0.8</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10">
+        <v>0.5</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>4</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2014</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>2015</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>2016</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>2017</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>2018</v>
-      </c>
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>2019</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>2020</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>2021</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>2022</v>
-      </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>2023</v>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>77</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13">
-        <v>2024</v>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>77</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
-        <v>2025</v>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>58</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15">
+        <v>0.8</v>
+      </c>
+      <c r="C15">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16">
+        <v>0.5</v>
+      </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>0.4</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -27799,6 +27746,215 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1A6ACA0-5BAF-4CF3-A9BA-46A30A6E0A57}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>2013</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2014</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>2015</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>2016</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>2017</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>2018</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>2019</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>2021</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>2022</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>2023</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>2025</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86AC6C15-2C38-4F0A-BF61-EE73FED61ED7}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -28073,7 +28229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F05C8F-316F-4046-A284-28124FE5A655}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -28209,7 +28365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EB23CA-A17F-4A62-9AC4-DA1175EB60E4}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
@@ -28349,7 +28505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA3DE9A-9DC8-9B4C-920E-613E1AA78E62}">
   <dimension ref="A1:HM126"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6"/>
